--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5E07194-76A2-490E-A685-76315C767B93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D24C8A-C08C-413B-BB03-0C2BCA9CB73B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0228648-5077-4973-A199-750C265DBE61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B763A1-CEBC-4937-B096-2FDDBFD17955}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08288224-1B06-403A-8BB1-64EEE412A68C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DC200B0-B60C-4E0D-9230-1B33DC6D0578}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D24C8A-C08C-413B-BB03-0C2BCA9CB73B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B6E9EE0-B7FB-4E82-90D6-BB032C1BAECD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B763A1-CEBC-4937-B096-2FDDBFD17955}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FBF6C74-E049-401E-B02E-C84E25EC36CC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DC200B0-B60C-4E0D-9230-1B33DC6D0578}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05DA9378-3C18-4CA6-A489-9331F883260A}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B6E9EE0-B7FB-4E82-90D6-BB032C1BAECD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B6DB041-E96C-4F0A-ADB7-B7623DA9A82D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FBF6C74-E049-401E-B02E-C84E25EC36CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A92ED83-C586-4452-964B-2E20376C7703}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05DA9378-3C18-4CA6-A489-9331F883260A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14A6A66B-3134-4E40-BFBA-DF35116B9AAD}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B6DB041-E96C-4F0A-ADB7-B7623DA9A82D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D21D0430-FF27-4E7A-99A8-8B8314737A21}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A92ED83-C586-4452-964B-2E20376C7703}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEB7DA9D-1755-4CE7-A2E1-959270A81DDC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14A6A66B-3134-4E40-BFBA-DF35116B9AAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA2EB71-0517-4CD1-97B1-D1D0BCA5E6D6}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D21D0430-FF27-4E7A-99A8-8B8314737A21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87176C1E-73A7-43D9-8C72-2E4742DE1E3C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEB7DA9D-1755-4CE7-A2E1-959270A81DDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEEBEBFE-A613-40A3-A356-F0AF57F753ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFA2EB71-0517-4CD1-97B1-D1D0BCA5E6D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4FCAA3-9464-4AEF-A4B3-95D6007CE260}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87176C1E-73A7-43D9-8C72-2E4742DE1E3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B314BE-289F-479F-8341-73AD3DDC9764}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEEBEBFE-A613-40A3-A356-F0AF57F753ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10780F0E-7C37-4DDF-9B20-E7E118C67533}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4FCAA3-9464-4AEF-A4B3-95D6007CE260}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D8418F-E803-4135-B300-BE494895A391}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6B314BE-289F-479F-8341-73AD3DDC9764}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{080FEB10-C5F8-425B-A82C-D637F5108A4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10780F0E-7C37-4DDF-9B20-E7E118C67533}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC72BCA3-6AFC-45BA-9713-DD0C71DA983C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D8418F-E803-4135-B300-BE494895A391}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4DCAEF8-7870-403F-BABC-703503C34923}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{080FEB10-C5F8-425B-A82C-D637F5108A4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475BF7C8-8883-4340-A2B3-1DA3F4A06905}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC72BCA3-6AFC-45BA-9713-DD0C71DA983C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B0B0B50-5E39-4ADC-A691-54DE729A1C8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4DCAEF8-7870-403F-BABC-703503C34923}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4718DDB4-7613-47F1-B410-A9ABD12A0156}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475BF7C8-8883-4340-A2B3-1DA3F4A06905}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E6471A-B13B-4617-916D-CC725AC1AEB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B0B0B50-5E39-4ADC-A691-54DE729A1C8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62995C2E-C7D7-4F1F-B01D-4B5440C30CDD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4718DDB4-7613-47F1-B410-A9ABD12A0156}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8794F4CD-44F9-4D89-A767-1DED45AB19B3}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E6471A-B13B-4617-916D-CC725AC1AEB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8C6194-940E-426F-A0EB-60DF96BC001B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62995C2E-C7D7-4F1F-B01D-4B5440C30CDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{993CB3C9-33CF-4EA0-9609-CC4CE113C575}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8794F4CD-44F9-4D89-A767-1DED45AB19B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E0ADB2-20AC-400F-A2C9-A018254B2299}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8C6194-940E-426F-A0EB-60DF96BC001B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42880573-3774-4742-B4C6-DF497FE66F7E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{993CB3C9-33CF-4EA0-9609-CC4CE113C575}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3AA6EE1-5AC5-48ED-AF0E-02D9FF509854}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E0ADB2-20AC-400F-A2C9-A018254B2299}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACC6EBC4-214E-4350-9F7C-ED7F01983FE1}"/>
 </file>
--- a/____EvoM1_TraitTable/innovation_reader.xlsx
+++ b/____EvoM1_TraitTable/innovation_reader.xlsx
@@ -9749,13 +9749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42880573-3774-4742-B4C6-DF497FE66F7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B559E89-6A73-49E5-8B40-9FC90D9C4446}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3AA6EE1-5AC5-48ED-AF0E-02D9FF509854}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC7E5881-33D8-43E7-A71E-F462616D98B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACC6EBC4-214E-4350-9F7C-ED7F01983FE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1241A006-6A6B-45C1-AC77-BFCAFDC5BD8F}"/>
 </file>